--- a/samples/R_长期借款明细表.xlsx
+++ b/samples/R_长期借款明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,18 +438,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,17 +475,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>借款日</t>
+          <t>借款日期</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>到期日</t>
+          <t>到期日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>年利率</t>
+          <t>年利率%</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -489,95 +495,286 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>已计利息</t>
+          <t>抵押/质押物</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>应计利息</t>
+          <t>本期还本</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>本期付息</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>期末余额</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>是否函证</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>函证结果</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>建设银行重庆分行</t>
+          <t>工商银行渝北支行</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>JK-2022-001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>5000000</v>
+          <t>CQ-001</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>10000000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2027-03-14</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.85</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>抵押-厂房</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>260000</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>260000</v>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>渝北区厂房(原值1200万)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>485000</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>三年期项目贷款</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>工商银行重庆分行</t>
+          <t>工商银行渝北支行</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>JK-2024-008</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+          <t>CQ-002</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>抵押+保证</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>设备抵押(净值500万)+担保</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>316667</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>本年新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>建设银行两江支行</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CQ-003</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>信用</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>245000</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2028-06-19</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>信用</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>122500</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>122500</v>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>本年归还本金200万</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>建设银行两江支行</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CQ-004</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>保证</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>重庆鑫源装备提供担保</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>77500</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>本年新增</t>
+        </is>
       </c>
     </row>
   </sheetData>
